--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,10 +453,10 @@
         <v>123</v>
       </c>
       <c r="D3">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>0</v>
